--- a/METADATA/sample_metadata_mapping.xlsx
+++ b/METADATA/sample_metadata_mapping.xlsx
@@ -1,27 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B857955-78E9-4EC5-ADE7-4564FB2C26C2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18350" windowHeight="6080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SHRIMP" sheetId="1" r:id="rId1"/>
     <sheet name="CRABS" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="321">
   <si>
     <t>SHRIMP</t>
   </si>
@@ -40,7 +47,7 @@
     <t>PHYLOGENETIC TREE</t>
   </si>
   <si>
-    <t>DATA GENBANK</t>
+    <t>DATA GENBANK (Specimen_voucher)</t>
   </si>
   <si>
     <t>MUSEUM CODE</t>
@@ -532,276 +539,288 @@
     <t>PV356789</t>
   </si>
   <si>
+    <t>M32J</t>
+  </si>
+  <si>
+    <t>barcode 65</t>
+  </si>
+  <si>
+    <t>barcode 27</t>
+  </si>
+  <si>
+    <t>M_sp_32_1031</t>
+  </si>
+  <si>
+    <t>Macrobrachium_PV356790</t>
+  </si>
+  <si>
+    <t>REEB_0556</t>
+  </si>
+  <si>
+    <t>IKIAM 1846</t>
+  </si>
+  <si>
+    <t>PV351734</t>
+  </si>
+  <si>
+    <t>PV356790</t>
+  </si>
+  <si>
+    <t>M33J</t>
+  </si>
+  <si>
+    <t>barcode 64</t>
+  </si>
+  <si>
+    <t>barcode 26</t>
+  </si>
+  <si>
+    <t>M_sp_33_1032</t>
+  </si>
+  <si>
+    <t>Macrobrachium_PV356791</t>
+  </si>
+  <si>
+    <t>REEB_0560</t>
+  </si>
+  <si>
+    <t>IKIAM 1847</t>
+  </si>
+  <si>
+    <t>PV351735</t>
+  </si>
+  <si>
+    <t>PV356791</t>
+  </si>
+  <si>
+    <t>M34J</t>
+  </si>
+  <si>
+    <t>barcode 63</t>
+  </si>
+  <si>
+    <t>barcode 24</t>
+  </si>
+  <si>
+    <t>M_sp_34_1033</t>
+  </si>
+  <si>
+    <t>Macrobrachium_PV356792</t>
+  </si>
+  <si>
+    <t>REEB_0539_1</t>
+  </si>
+  <si>
+    <t>IKIAM 1830</t>
+  </si>
+  <si>
+    <t>PV351736</t>
+  </si>
+  <si>
+    <t>PV356792</t>
+  </si>
+  <si>
+    <t>M35J</t>
+  </si>
+  <si>
+    <t>barcode 62</t>
+  </si>
+  <si>
+    <t>barcode 23</t>
+  </si>
+  <si>
+    <t>M_sp_35_1034</t>
+  </si>
+  <si>
+    <t>Macrobrachium_PV356793</t>
+  </si>
+  <si>
+    <t>REEB_0539_2</t>
+  </si>
+  <si>
+    <t>PV351737</t>
+  </si>
+  <si>
+    <t>PV356793</t>
+  </si>
+  <si>
+    <t>M36J</t>
+  </si>
+  <si>
+    <t>barcode 61</t>
+  </si>
+  <si>
+    <t>barcode 22</t>
+  </si>
+  <si>
+    <t>M_sp_36_1035</t>
+  </si>
+  <si>
+    <t>Macrobrachium_PV356794</t>
+  </si>
+  <si>
+    <t>REEB_0539_3</t>
+  </si>
+  <si>
+    <t>PV351738</t>
+  </si>
+  <si>
+    <t>PV356794</t>
+  </si>
+  <si>
+    <t>CRABS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA RAW ( NGSpeciesID)	</t>
+  </si>
+  <si>
+    <t>Second time</t>
+  </si>
+  <si>
+    <t>CM01</t>
+  </si>
+  <si>
+    <t>barcode 21</t>
+  </si>
+  <si>
+    <t>Trichodactylidae_REEB_0541</t>
+  </si>
+  <si>
+    <t>Trichodactylidae_PV764581</t>
+  </si>
+  <si>
+    <t>REEB 0541</t>
+  </si>
+  <si>
+    <t>REEB 0553</t>
+  </si>
+  <si>
+    <t>IKIAM 1845</t>
+  </si>
+  <si>
+    <t>PV746806</t>
+  </si>
+  <si>
+    <t>PV764581</t>
+  </si>
+  <si>
+    <t>CM02</t>
+  </si>
+  <si>
+    <t>barcode 20</t>
+  </si>
+  <si>
+    <t>Trichodactylidae_REEB_0539</t>
+  </si>
+  <si>
+    <t>Trichodactylidae_PV764587</t>
+  </si>
+  <si>
+    <t>REEB 0539</t>
+  </si>
+  <si>
+    <t>REEB 0524</t>
+  </si>
+  <si>
+    <t>IKIAM 1831</t>
+  </si>
+  <si>
+    <t>PV746812</t>
+  </si>
+  <si>
+    <t>PV764587</t>
+  </si>
+  <si>
+    <t>CM03</t>
+  </si>
+  <si>
+    <t>barcode 19</t>
+  </si>
+  <si>
+    <t>Trichodactylidae_REEB_0505</t>
+  </si>
+  <si>
+    <t>Trichodactylidae_PV764582</t>
+  </si>
+  <si>
+    <t>REEB 0505</t>
+  </si>
+  <si>
+    <t>IKIAM 1809</t>
+  </si>
+  <si>
+    <t>PV746807</t>
+  </si>
+  <si>
+    <t>PV764582</t>
+  </si>
+  <si>
+    <t>CM05</t>
+  </si>
+  <si>
+    <t>barcode 05</t>
+  </si>
+  <si>
+    <t>CM05_257</t>
+  </si>
+  <si>
+    <t>CM05_0004</t>
+  </si>
+  <si>
+    <t>Pseudothelphusidae_PV759701</t>
+  </si>
+  <si>
+    <t>REEB 0566</t>
+  </si>
+  <si>
+    <t>IKIAM 1851</t>
+  </si>
+  <si>
+    <t>PV839498</t>
+  </si>
+  <si>
+    <t>PV759701</t>
+  </si>
+  <si>
+    <t>CM06</t>
+  </si>
+  <si>
+    <t>barcode 04</t>
+  </si>
+  <si>
     <t>barcode 29</t>
   </si>
   <si>
+    <t>Trichodactylidae_REEB_0547</t>
+  </si>
+  <si>
+    <t>Trichodactylidae_PV764584</t>
+  </si>
+  <si>
+    <t>REEB 0547</t>
+  </si>
+  <si>
+    <t>REEB 0526</t>
+  </si>
+  <si>
+    <t>IKIAM 1839</t>
+  </si>
+  <si>
+    <t>PV746809</t>
+  </si>
+  <si>
+    <t>PV764584</t>
+  </si>
+  <si>
+    <t>CM07</t>
+  </si>
+  <si>
+    <t>barcode 03</t>
+  </si>
+  <si>
     <t>barcode 28</t>
   </si>
   <si>
-    <t>M32J</t>
-  </si>
-  <si>
-    <t>barcode 65</t>
-  </si>
-  <si>
-    <t>barcode 27</t>
-  </si>
-  <si>
-    <t>M_sp_32_1031</t>
-  </si>
-  <si>
-    <t>Macrobrachium_PV356790</t>
-  </si>
-  <si>
-    <t>REEB_0556</t>
-  </si>
-  <si>
-    <t>IKIAM 1846</t>
-  </si>
-  <si>
-    <t>PV351734</t>
-  </si>
-  <si>
-    <t>PV356790</t>
-  </si>
-  <si>
-    <t>M33J</t>
-  </si>
-  <si>
-    <t>barcode 64</t>
-  </si>
-  <si>
-    <t>barcode 26</t>
-  </si>
-  <si>
-    <t>M_sp_33_1032</t>
-  </si>
-  <si>
-    <t>Macrobrachium_PV356791</t>
-  </si>
-  <si>
-    <t>REEB_0560</t>
-  </si>
-  <si>
-    <t>IKIAM 1847</t>
-  </si>
-  <si>
-    <t>PV351735</t>
-  </si>
-  <si>
-    <t>PV356791</t>
-  </si>
-  <si>
-    <t>M34J</t>
-  </si>
-  <si>
-    <t>barcode 63</t>
-  </si>
-  <si>
-    <t>barcode 24</t>
-  </si>
-  <si>
-    <t>M_sp_34_1033</t>
-  </si>
-  <si>
-    <t>Macrobrachium_PV356792</t>
-  </si>
-  <si>
-    <t>REEB_0539_1</t>
-  </si>
-  <si>
-    <t>IKIAM 1830</t>
-  </si>
-  <si>
-    <t>PV351736</t>
-  </si>
-  <si>
-    <t>PV356792</t>
-  </si>
-  <si>
-    <t>M35J</t>
-  </si>
-  <si>
-    <t>barcode 62</t>
-  </si>
-  <si>
-    <t>barcode 23</t>
-  </si>
-  <si>
-    <t>M_sp_35_1034</t>
-  </si>
-  <si>
-    <t>Macrobrachium_PV356793</t>
-  </si>
-  <si>
-    <t>REEB_0539_2</t>
-  </si>
-  <si>
-    <t>PV351737</t>
-  </si>
-  <si>
-    <t>PV356793</t>
-  </si>
-  <si>
-    <t>M36J</t>
-  </si>
-  <si>
-    <t>barcode 61</t>
-  </si>
-  <si>
-    <t>barcode 22</t>
-  </si>
-  <si>
-    <t>M_sp_36_1035</t>
-  </si>
-  <si>
-    <t>Macrobrachium_PV356794</t>
-  </si>
-  <si>
-    <t>REEB_0539_3</t>
-  </si>
-  <si>
-    <t>PV351738</t>
-  </si>
-  <si>
-    <t>PV356794</t>
-  </si>
-  <si>
-    <t>CRABS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DATA RAW ( NGSpeciesID)	</t>
-  </si>
-  <si>
-    <t>DATA GENBANK (Field code)</t>
-  </si>
-  <si>
-    <t>Primera vez</t>
-  </si>
-  <si>
-    <t>Segunda Vez</t>
-  </si>
-  <si>
-    <t>CM01</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_REEB_0541</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_PV764581</t>
-  </si>
-  <si>
-    <t>REEB 0541</t>
-  </si>
-  <si>
-    <t>REEB 0553</t>
-  </si>
-  <si>
-    <t>IKIAM 1845</t>
-  </si>
-  <si>
-    <t>PV746806</t>
-  </si>
-  <si>
-    <t>PV764581</t>
-  </si>
-  <si>
-    <t>CM02</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_REEB_0539</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_PV764587</t>
-  </si>
-  <si>
-    <t>REEB 0539</t>
-  </si>
-  <si>
-    <t>REEB 0524</t>
-  </si>
-  <si>
-    <t>IKIAM 1831</t>
-  </si>
-  <si>
-    <t>PV746812</t>
-  </si>
-  <si>
-    <t>PV764587</t>
-  </si>
-  <si>
-    <t>CM03</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_REEB_0505</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_PV764582</t>
-  </si>
-  <si>
-    <t>REEB 0505</t>
-  </si>
-  <si>
-    <t>IKIAM 1809</t>
-  </si>
-  <si>
-    <t>PV746807</t>
-  </si>
-  <si>
-    <t>PV764582</t>
-  </si>
-  <si>
-    <t>CM05</t>
-  </si>
-  <si>
-    <t>CM05_257</t>
-  </si>
-  <si>
-    <t>CM05_0004</t>
-  </si>
-  <si>
-    <t>Pseudothelphusidae_PV759701</t>
-  </si>
-  <si>
-    <t>REEB 0566</t>
-  </si>
-  <si>
-    <t>IKIAM 1851</t>
-  </si>
-  <si>
-    <t>PV839498</t>
-  </si>
-  <si>
-    <t>PV759701</t>
-  </si>
-  <si>
-    <t>CM06</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_REEB_0547</t>
-  </si>
-  <si>
-    <t>Trichodactylidae_PV764584</t>
-  </si>
-  <si>
-    <t>REEB 0547</t>
-  </si>
-  <si>
-    <t>REEB 0526</t>
-  </si>
-  <si>
-    <t>IKIAM 1839</t>
-  </si>
-  <si>
-    <t>PV746809</t>
-  </si>
-  <si>
-    <t>PV764584</t>
-  </si>
-  <si>
-    <t>CM07</t>
-  </si>
-  <si>
     <t>CM07_234</t>
   </si>
   <si>
@@ -826,6 +845,9 @@
     <t>CM08</t>
   </si>
   <si>
+    <t>barcode 02</t>
+  </si>
+  <si>
     <t>Trichodactylidae_REEB_0565</t>
   </si>
   <si>
@@ -847,6 +869,9 @@
     <t>CM09</t>
   </si>
   <si>
+    <t>barcode 12</t>
+  </si>
+  <si>
     <t>Trichodactylidae_REEB_0548</t>
   </si>
   <si>
@@ -868,6 +893,12 @@
     <t>CM10</t>
   </si>
   <si>
+    <t>barcode 11</t>
+  </si>
+  <si>
+    <t>barcode 25</t>
+  </si>
+  <si>
     <t>CM10_252</t>
   </si>
   <si>
@@ -892,6 +923,9 @@
     <t>CM11</t>
   </si>
   <si>
+    <t>barcode 10</t>
+  </si>
+  <si>
     <t>Trichodactylidae_REEB_0504</t>
   </si>
   <si>
@@ -913,6 +947,9 @@
     <t>CM13</t>
   </si>
   <si>
+    <t>barcode 08</t>
+  </si>
+  <si>
     <t>CM13_249</t>
   </si>
   <si>
@@ -937,6 +974,9 @@
     <t>CM14</t>
   </si>
   <si>
+    <t>barcode 07</t>
+  </si>
+  <si>
     <t>Trichodactylidae_REEB_0561</t>
   </si>
   <si>
@@ -953,56 +993,24 @@
   </si>
   <si>
     <t>PV764586</t>
-  </si>
-  <si>
-    <t>barcode 21</t>
-  </si>
-  <si>
-    <t>barcode 20</t>
-  </si>
-  <si>
-    <t>barcode 19</t>
-  </si>
-  <si>
-    <t>barcode 05</t>
-  </si>
-  <si>
-    <t>barcode 04</t>
-  </si>
-  <si>
-    <t>barcode 03</t>
-  </si>
-  <si>
-    <t>barcode 02</t>
-  </si>
-  <si>
-    <t>barcode 12</t>
-  </si>
-  <si>
-    <t>barcode 11</t>
-  </si>
-  <si>
-    <t>barcode 10</t>
-  </si>
-  <si>
-    <t>barcode 08</t>
-  </si>
-  <si>
-    <t>barcode 07</t>
-  </si>
-  <si>
-    <t>barcode 25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1010,59 +1018,206 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1075,8 +1230,194 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1109,6 +1450,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -1119,19 +1473,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1162,125 +1503,392 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Coma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
+    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
+    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
+    <cellStyle name="Nota" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Salida" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
+    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
+    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
+    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
+    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
+    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
+    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
+    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1475,1462 +2083,1463 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="B2:L27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" customWidth="1"/>
-    <col min="7" max="7" width="25.26953125" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" customWidth="1"/>
-    <col min="9" max="9" width="16.90625" customWidth="1"/>
+    <col min="2" max="2" width="15.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="16.2727272727273" customWidth="1"/>
+    <col min="6" max="6" width="16.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="25.2727272727273" customWidth="1"/>
+    <col min="8" max="8" width="15.1818181818182" customWidth="1"/>
+    <col min="9" max="9" width="16.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="22" t="s">
+    <row r="2" ht="13" spans="2:12">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="23"/>
-    </row>
-    <row r="3" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="20" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" ht="13" spans="2:12">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="20" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="23"/>
-    </row>
-    <row r="4" spans="2:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="21"/>
-      <c r="C4" s="1" t="s">
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" ht="53.25" customHeight="1" spans="2:12">
+      <c r="B4" s="7"/>
+      <c r="C4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="1" t="s">
+      <c r="G4" s="7"/>
+      <c r="H4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="21"/>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="7"/>
+      <c r="K4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
+    <row r="5" ht="12.5" spans="2:12">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
+    <row r="6" ht="12.5" spans="2:12">
+      <c r="B6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="27" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="27" t="s">
+    <row r="7" ht="12.5" spans="2:12">
+      <c r="B7" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
+    <row r="8" ht="12.5" spans="2:12">
+      <c r="B8" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="27" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
+    <row r="9" ht="12.5" spans="2:12">
+      <c r="B9" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
+    <row r="10" ht="12.5" spans="2:12">
+      <c r="B10" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="27" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="27" t="s">
+    <row r="11" ht="12.5" spans="2:12">
+      <c r="B11" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="27" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
+    <row r="12" ht="12.5" spans="2:12">
+      <c r="B12" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="H12" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="27" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+    <row r="13" ht="12.5" spans="2:12">
+      <c r="B13" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+    <row r="14" ht="12.5" spans="2:12">
+      <c r="B14" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="H14" s="29" t="s">
+      <c r="H14" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="27" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+    <row r="15" ht="12.5" spans="2:12">
+      <c r="B15" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="H15" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="L15" s="27" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+    <row r="16" ht="12.5" spans="2:12">
+      <c r="B16" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="29" t="s">
+      <c r="H16" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="27" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+    <row r="17" ht="12.5" spans="2:12">
+      <c r="B17" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="27" t="s">
+      <c r="J17" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="L17" s="27" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+    <row r="18" ht="12.5" spans="2:12">
+      <c r="B18" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="L18" s="27" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+    <row r="19" ht="12.5" spans="2:12">
+      <c r="B19" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I19" s="29" t="s">
+      <c r="I19" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="L19" s="28" t="s">
+      <c r="L19" s="31" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+    <row r="20" ht="12.5" spans="2:12">
+      <c r="B20" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="H20" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="K20" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="L20" s="28" t="s">
+      <c r="L20" s="31" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+    <row r="21" ht="12.5" spans="2:12">
+      <c r="B21" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="29" t="s">
+      <c r="H21" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="I21" s="29" t="s">
+      <c r="I21" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="K21" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="L21" s="27" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+    <row r="22" ht="12.5" spans="2:12">
+      <c r="B22" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="H22" s="29" t="s">
+      <c r="H22" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="I22" s="29" t="s">
+      <c r="I22" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="27" t="s">
+      <c r="J22" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="K22" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="L22" s="27" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+    <row r="23" ht="12.5" spans="2:12">
+      <c r="B23" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="E23" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="F23" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="H23" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="I23" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="J23" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H23" s="29" t="s">
+      <c r="K23" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="I23" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="J23" s="27" t="s">
+      <c r="L23" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="K23" s="8" t="s">
+    </row>
+    <row r="24" ht="12.5" spans="2:12">
+      <c r="B24" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="C24" s="25" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="24" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="E24" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="F24" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="H24" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="I24" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="J24" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="H24" s="29" t="s">
+      <c r="K24" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="I24" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="J24" s="27" t="s">
+      <c r="L24" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="K24" s="8" t="s">
+    </row>
+    <row r="25" ht="12.5" spans="2:12">
+      <c r="B25" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="C25" s="25" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="25" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="D25" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="E25" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="F25" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="H25" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="I25" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="J25" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="H25" s="29" t="s">
+      <c r="K25" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="I25" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="J25" s="27" t="s">
+      <c r="L25" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="K25" s="8" t="s">
+    </row>
+    <row r="26" ht="12.5" spans="2:12">
+      <c r="B26" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="C26" s="25" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="26" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="E26" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="F26" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="H26" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="I26" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="J26" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="H26" s="29" t="s">
+      <c r="L26" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="I26" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="J26" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="K26" s="8" t="s">
+    </row>
+    <row r="27" ht="12.5" spans="2:12">
+      <c r="B27" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="L26" s="8" t="s">
+      <c r="C27" s="25" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="27" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="E27" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="F27" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="G27" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="H27" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="I27" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="J27" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="K27" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="H27" s="29" t="s">
+      <c r="L27" s="27" t="s">
         <v>211</v>
-      </c>
-      <c r="I27" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="J27" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:L2"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="B2:L25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="5" max="5" width="28.90625" customWidth="1"/>
-    <col min="6" max="6" width="27.36328125" customWidth="1"/>
-    <col min="7" max="7" width="27.08984375" customWidth="1"/>
+    <col min="2" max="2" width="14.4545454545455" customWidth="1"/>
+    <col min="5" max="5" width="28.9090909090909" customWidth="1"/>
+    <col min="6" max="6" width="27.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="27.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
+    <row r="2" ht="13" spans="2:12">
+      <c r="B2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" ht="13" spans="2:12">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" spans="2:12">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="23"/>
-    </row>
-    <row r="3" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="J4" s="7"/>
+      <c r="K4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="12.5" spans="2:12">
+      <c r="B5" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="26" t="s">
+      <c r="C5" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="23"/>
-    </row>
-    <row r="4" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="21"/>
-      <c r="C4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="9" t="s">
+      <c r="D5" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="F5" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="J4" s="21"/>
-      <c r="K4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
+      <c r="H5" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="11" t="s">
+      <c r="I5" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="G5" s="12" t="s">
+      <c r="J5" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="K5" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="L5" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="J5" s="11" t="s">
+    </row>
+    <row r="6" ht="12.5" spans="2:12">
+      <c r="B6" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="C6" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="D6" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
+      <c r="F6" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="11" t="s">
+      <c r="H6" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="J6" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="K6" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="L6" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="K6" s="14" t="s">
+    </row>
+    <row r="7" ht="12.5" spans="2:12">
+      <c r="B7" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="C7" s="10" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+      <c r="D7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>312</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="I7" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="I7" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="K7" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="L7" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="L7" s="14" t="s">
+    </row>
+    <row r="8" ht="12.5" spans="2:12">
+      <c r="B8" s="9" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="20" t="s">
         <v>246</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="19" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
+    <row r="9" ht="12.5" spans="2:12">
+      <c r="B9" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" ht="12.5" spans="2:12">
+      <c r="B10" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" ht="12.5" spans="2:12">
+      <c r="B11" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" ht="12.5" spans="2:12">
+      <c r="B12" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" ht="12.5" spans="2:12">
+      <c r="B13" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" ht="12.5" spans="2:12">
+      <c r="B14" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" ht="12.5" spans="2:12">
+      <c r="B15" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" ht="12.5" spans="2:12">
+      <c r="B16" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="D9" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="36" t="s">
+      <c r="D16" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="D10" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C11" s="36" t="s">
+      <c r="F16" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="D11" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="C12" s="35" t="s">
+      <c r="H16" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="D12" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" s="35" t="s">
+      <c r="I16" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D13" s="35" t="s">
-        <v>322</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C14" s="35" t="s">
+      <c r="K16" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="C15" s="35" t="s">
+      <c r="L16" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="D16" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="17" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I21" s="19"/>
-    </row>
-    <row r="22" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I22" s="19"/>
-    </row>
-    <row r="23" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I24" s="19"/>
-    </row>
-    <row r="25" spans="9:9" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="I25" s="19"/>
+    </row>
+    <row r="17" ht="12.5" spans="9:9">
+      <c r="I17" s="21"/>
+    </row>
+    <row r="18" ht="12.5" spans="9:9">
+      <c r="I18" s="21"/>
+    </row>
+    <row r="19" ht="12.5" spans="9:9">
+      <c r="I19" s="21"/>
+    </row>
+    <row r="20" ht="12.5" spans="9:9">
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" ht="12.5" spans="9:9">
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" ht="12.5" spans="9:9">
+      <c r="I22" s="21"/>
+    </row>
+    <row r="23" ht="12.5" spans="9:9">
+      <c r="I23" s="21"/>
+    </row>
+    <row r="24" ht="12.5" spans="9:9">
+      <c r="I24" s="21"/>
+    </row>
+    <row r="25" ht="12.5" spans="9:9">
+      <c r="I25" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:L2"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>